--- a/suddivisioneLavoro.xlsx
+++ b/suddivisioneLavoro.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>mora</t>
   </si>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t>revisione</t>
+  </si>
+  <si>
+    <t>DiagrammaUML</t>
+  </si>
+  <si>
+    <t>Documentazione</t>
   </si>
 </sst>
 </file>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -129,6 +135,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -425,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:N9"/>
+  <dimension ref="A2:N11"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -512,13 +524,31 @@
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="8"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B11" s="5">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C11" s="5">
         <v>9</v>
       </c>
     </row>
